--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_298_R30.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_298_R30.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9733</v>
+        <v>2.0275</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9791</v>
+        <v>0.0669</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9942</v>
+        <v>1.9606</v>
       </c>
       <c r="G2" t="n">
         <v>2.0284</v>
@@ -610,13 +610,13 @@
         <v>3.4793</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3366</v>
+        <v>1.3908</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4065</v>
+        <v>1.4943</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0698</v>
+        <v>-0.1034</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1713</v>
+        <v>1.5326</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7024</v>
+        <v>2.131</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5311</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0905</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.666</v>
+        <v>-0.3047</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3655</v>
+        <v>0.063</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3005</v>
+        <v>-0.3677</v>
       </c>
       <c r="V3" t="n">
         <v>0.5361</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7769</v>
+        <v>1.0106</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1731</v>
+        <v>0.4404</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6037</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0.9516</v>
@@ -766,13 +766,13 @@
         <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2016</v>
+        <v>0.4353</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1494</v>
+        <v>0.118</v>
       </c>
       <c r="U4" t="n">
-        <v>0.351</v>
+        <v>0.3174</v>
       </c>
       <c r="V4" t="n">
         <v>-1.0722</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3659</v>
+        <v>-0.5286</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1001</v>
+        <v>0.2062</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.466</v>
+        <v>-0.7349</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5729</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1195</v>
+        <v>-0.0433</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1845</v>
+        <v>-0.0784</v>
       </c>
       <c r="U5" t="n">
-        <v>0.304</v>
+        <v>0.0351</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0722</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1658</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7101</v>
+        <v>-1.1204</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5444</v>
+        <v>0.3427</v>
       </c>
       <c r="G6" t="n">
         <v>-3.1031</v>
@@ -922,13 +922,13 @@
         <v>2.3195</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1502</v>
+        <v>0.2379</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1336</v>
+        <v>0.4562</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0167</v>
+        <v>-0.2183</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6689</v>
+        <v>-1.2905</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2203</v>
+        <v>-0.2217</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4485</v>
+        <v>-1.0689</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6392</v>
+        <v>-2.5382</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0708</v>
+        <v>-0.4537</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4316</v>
+        <v>-2.0844</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3277</v>
+        <v>0.1277</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.502</v>
+        <v>0.1043</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1742</v>
+        <v>0.0234</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3115</v>
+        <v>-2.6659</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5688</v>
+        <v>-0.5581</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7426</v>
+        <v>-2.1078</v>
       </c>
       <c r="P7" t="n">
+        <v>2.5515</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.4639</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-2.3195</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>3.0154</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1507</v>
+        <v>-0.3734</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5351</v>
+        <v>-0.0272</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3844</v>
+        <v>-0.3462</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2836</v>
+        <v>-0.9304</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8919</v>
+        <v>0.1418</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4433</v>
+        <v>-2.1861</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.24</v>
+        <v>-0.704</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2033</v>
+        <v>-1.4821</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5382</v>
+        <v>-1.6392</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4537</v>
+        <v>-2.0708</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0844</v>
+        <v>0.4316</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1277</v>
+        <v>-0.3277</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1043</v>
+        <v>-1.502</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0234</v>
+        <v>1.1742</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6659</v>
+        <v>-1.3115</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5581</v>
+        <v>-0.5688</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1078</v>
+        <v>-0.7426</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5515</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.4639</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>3.0154</v>
+        <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5261</v>
+        <v>-0.3666</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0455</v>
+        <v>0.0514</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4806</v>
+        <v>-0.418</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9304</v>
+        <v>0.2836</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1418</v>
+        <v>1.8919</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7342</v>
+        <v>-2.6256</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7612</v>
+        <v>-0.3169</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.973</v>
+        <v>-2.3087</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8969</v>
+        <v>-0.1694</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4753</v>
+        <v>-0.9423</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3722</v>
+        <v>0.7729</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4357</v>
+        <v>2.318</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5615</v>
+        <v>-0.1947</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.9973</v>
+        <v>2.5127</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4612</v>
+        <v>-2.4874</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0862</v>
+        <v>-0.7477</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.375</v>
+        <v>-1.7398</v>
       </c>
       <c r="P9" t="n">
-        <v>0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.7834</v>
+        <v>-3.9432</v>
       </c>
       <c r="R9" t="n">
-        <v>3.0154</v>
+        <v>2.3195</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0693</v>
+        <v>-0.8325</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3857</v>
+        <v>0.2361</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.455</v>
+        <v>-1.0686</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7643</v>
+        <v>-3.0253</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3989</v>
+        <v>-2.0523</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3654</v>
+        <v>-0.973</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2876</v>
+        <v>-1.8969</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3767</v>
+        <v>0.4753</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.6643</v>
+        <v>-2.3722</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2001</v>
+        <v>-0.4357</v>
       </c>
       <c r="K10" t="n">
-        <v>1.6203</v>
+        <v>0.5615</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8204</v>
+        <v>-0.9973</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.0874</v>
+        <v>-1.4612</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2435</v>
+        <v>-0.0862</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.8439</v>
+        <v>-1.375</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.0154</v>
+        <v>0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.0307</v>
+        <v>-2.7834</v>
       </c>
       <c r="R10" t="n">
         <v>3.0154</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2524</v>
+        <v>-1.3603</v>
       </c>
       <c r="T10" t="n">
-        <v>1.404</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1516</v>
+        <v>-1.455</v>
       </c>
       <c r="V10" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.428</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5595</v>
+        <v>-3.3473</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2172</v>
+        <v>-3.1499</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3423</v>
+        <v>-0.1974</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1694</v>
+        <v>-3.2876</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9423</v>
+        <v>1.3767</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7729</v>
+        <v>-4.6643</v>
       </c>
       <c r="J11" t="n">
-        <v>2.318</v>
+        <v>-0.2001</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1947</v>
+        <v>1.6203</v>
       </c>
       <c r="L11" t="n">
-        <v>2.5127</v>
+        <v>-1.8204</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.4874</v>
+        <v>-3.0874</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7477</v>
+        <v>-0.2435</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7398</v>
+        <v>-2.8439</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6237</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9432</v>
+        <v>-6.0307</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3195</v>
+        <v>3.0154</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7664</v>
+        <v>0.6695</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6642</v>
+        <v>0.653</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1022</v>
+        <v>0.0165</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0722</v>
+        <v>2.428</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5281</v>
+        <v>-5.6044</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6609</v>
+        <v>-4.0397</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8672</v>
+        <v>-1.5647</v>
       </c>
       <c r="G12" t="n">
         <v>-6.2819</v>
@@ -1390,13 +1390,13 @@
         <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2435</v>
+        <v>-1.3199</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2617</v>
+        <v>-0.6405</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9818</v>
+        <v>-0.6794</v>
       </c>
       <c r="V12" t="n">
         <v>0.1418</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.3085</v>
+        <v>-14.8148</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.2539</v>
+        <v>-8.760400000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.054500000000001</v>
+        <v>-6.0546</v>
       </c>
       <c r="G13" t="n">
         <v>-16.5997</v>
@@ -1468,19 +1468,19 @@
         <v>24.3551</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.3607</v>
+        <v>-1.8672</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9268999999999996</v>
+        <v>2.4206</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.2876</v>
+        <v>-4.287599999999999</v>
       </c>
       <c r="V13" t="n">
         <v>0.1728999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>8.356199999999999</v>
+        <v>8.356200000000001</v>
       </c>
       <c r="X13" t="n">
         <v>-8.183300000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. WILLIS</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3758</v>
+        <v>3.5789</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0493</v>
+        <v>0.6476</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3266</v>
+        <v>2.9313</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1145</v>
+        <v>0.5481</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0035</v>
+        <v>0.3339</v>
       </c>
       <c r="I14" t="n">
-        <v>2.118</v>
+        <v>0.2142</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7214</v>
+        <v>0.1442</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3865</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3349</v>
+        <v>0.0602</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3931</v>
+        <v>0.4039</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.39</v>
+        <v>0.2499</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7831</v>
+        <v>0.154</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1598</v>
+        <v>2.3195</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2434</v>
+        <v>0.8531</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6721</v>
+        <v>0.5034</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9155</v>
+        <v>0.3497</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1418</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>D. WILLIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2736</v>
+        <v>2.8217</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7836</v>
+        <v>1.1672</v>
       </c>
       <c r="F15" t="n">
-        <v>2.49</v>
+        <v>1.6544</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4624</v>
+        <v>2.1145</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7588</v>
+        <v>-0.0035</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7036</v>
+        <v>2.118</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1655</v>
+        <v>1.7214</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0371</v>
+        <v>0.3865</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1284</v>
+        <v>1.3349</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2968</v>
+        <v>0.3931</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7217</v>
+        <v>-0.39</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4248</v>
+        <v>0.7831</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.2473</v>
+        <v>1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.7988</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5515</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1307</v>
+        <v>-0.3108</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4169</v>
+        <v>-0.5542</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7139</v>
+        <v>0.2434</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2644</v>
+        <v>2.8187</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6476</v>
+        <v>1.5747</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6167</v>
+        <v>1.244</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5481</v>
+        <v>-0.3205</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3339</v>
+        <v>0.0409</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2142</v>
+        <v>-0.3614</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1442</v>
+        <v>0.462</v>
       </c>
       <c r="K16" t="n">
         <v>0.08400000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0602</v>
+        <v>0.378</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4039</v>
+        <v>-0.7825</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2499</v>
+        <v>-0.0431</v>
       </c>
       <c r="O16" t="n">
-        <v>0.154</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5386</v>
+        <v>1.2836</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5034</v>
+        <v>1.1127</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0351</v>
+        <v>0.1709</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6044</v>
+        <v>2.5544</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6638</v>
+        <v>2.7817</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0594</v>
+        <v>-0.2274</v>
       </c>
       <c r="G17" t="n">
         <v>1.7219</v>
@@ -1780,13 +1780,13 @@
         <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3465</v>
+        <v>1.2964</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0262</v>
+        <v>1.1442</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3203</v>
+        <v>0.1522</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2011</v>
+        <v>1.6152</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3388</v>
+        <v>0.0728</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8623</v>
+        <v>1.5423</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3205</v>
+        <v>1.4966</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0409</v>
+        <v>1.8749</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3614</v>
+        <v>-0.3782</v>
       </c>
       <c r="J18" t="n">
-        <v>0.462</v>
+        <v>1.6612</v>
       </c>
       <c r="K18" t="n">
-        <v>0.08400000000000001</v>
+        <v>2.6117</v>
       </c>
       <c r="L18" t="n">
-        <v>0.378</v>
+        <v>-0.9505</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7825</v>
+        <v>-0.1646</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0431</v>
+        <v>-0.7369</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7393999999999999</v>
+        <v>0.5723</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8556</v>
+        <v>-3.9432</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-5.7988</v>
       </c>
       <c r="R18" t="n">
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>0.666</v>
+        <v>-0.2271</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8768</v>
+        <v>-0.0784</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2109</v>
+        <v>-0.1487</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.2888</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>4.2888</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6919</v>
+        <v>1.5226</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8143</v>
+        <v>0.3425</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8776</v>
+        <v>1.1801</v>
       </c>
       <c r="G19" t="n">
         <v>0.6446</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1142</v>
+        <v>-0.3576</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6752</v>
+        <v>-0.3727</v>
       </c>
       <c r="V19" t="n">
         <v>1.6083</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>J. RHODEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8244</v>
+        <v>1.0565</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.281</v>
+        <v>1.0564</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1054</v>
+        <v>0.0001</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4966</v>
+        <v>3.8277</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8749</v>
+        <v>1.3853</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3782</v>
+        <v>2.4424</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6612</v>
+        <v>4.4135</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6117</v>
+        <v>0.8101</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9505</v>
+        <v>3.6034</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1646</v>
+        <v>-0.5858</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7369</v>
+        <v>0.5752</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5723</v>
+        <v>-1.1609</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.9432</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.7988</v>
+        <v>-4.639</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0179</v>
+        <v>1.5303</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4323</v>
+        <v>1.2819</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5856</v>
+        <v>0.2484</v>
       </c>
       <c r="V20" t="n">
-        <v>4.2888</v>
+        <v>-1.7501</v>
       </c>
       <c r="W20" t="n">
-        <v>4.2888</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6858</v>
+        <v>0.9553</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7433</v>
+        <v>0.9792</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0574</v>
+        <v>-0.0238</v>
       </c>
       <c r="G21" t="n">
         <v>1.7492</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0117</v>
+        <v>-0.7422</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7468</v>
+        <v>-0.5109</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2649</v>
+        <v>-0.2313</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2836</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. RHODEN</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3938</v>
+        <v>0.8265</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5846</v>
+        <v>-1.3395</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1907</v>
+        <v>2.166</v>
       </c>
       <c r="G22" t="n">
-        <v>3.8277</v>
+        <v>3.4624</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3853</v>
+        <v>0.7588</v>
       </c>
       <c r="I22" t="n">
-        <v>2.4424</v>
+        <v>2.7036</v>
       </c>
       <c r="J22" t="n">
-        <v>4.4135</v>
+        <v>3.1655</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8101</v>
+        <v>0.0371</v>
       </c>
       <c r="L22" t="n">
-        <v>3.6034</v>
+        <v>3.1284</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5858</v>
+        <v>0.2968</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5752</v>
+        <v>0.7217</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1609</v>
+        <v>-0.4248</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.5515</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.639</v>
+        <v>-5.7988</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8676</v>
+        <v>1.6836</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8101</v>
+        <v>1.2937</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0576</v>
+        <v>0.3899</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7501</v>
+        <v>-1.0722</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7501</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3227</v>
+        <v>0.7492</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0892</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.2245</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3809</v>
+        <v>2.1834</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0768</v>
+        <v>1.1932</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6959</v>
+        <v>0.9902</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.649</v>
+        <v>2.2865</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5055</v>
+        <v>0.2927</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8564000000000001</v>
+        <v>1.9939</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2681</v>
+        <v>-0.1032</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4287</v>
+        <v>0.9005</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1605</v>
+        <v>-1.0037</v>
       </c>
       <c r="P23" t="n">
-        <v>2.0876</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R23" t="n">
         <v>2.0876</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8153</v>
+        <v>0.3519</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4402</v>
+        <v>0.5034</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3752</v>
+        <v>-0.1516</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.214</v>
+        <v>-0.3943</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.214</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8393</v>
+        <v>0.4573</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7816</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0577</v>
+        <v>1.1927</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4471</v>
+        <v>-0.3809</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5041</v>
+        <v>-1.0768</v>
       </c>
       <c r="I24" t="n">
-        <v>0.057</v>
+        <v>0.6959</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1067</v>
+        <v>-0.649</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1141</v>
+        <v>-1.5055</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2208</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5538</v>
+        <v>0.2681</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.39</v>
+        <v>0.4287</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1638</v>
+        <v>-0.1605</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2161</v>
+        <v>-0.0354</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2715</v>
+        <v>-0.0863</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0553</v>
+        <v>0.051</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.845</v>
+        <v>-1.0752</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4189</v>
+        <v>-1.0175</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4261</v>
+        <v>-0.0577</v>
       </c>
       <c r="G25" t="n">
-        <v>2.1834</v>
+        <v>-0.4471</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1932</v>
+        <v>-0.5041</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9902</v>
+        <v>0.057</v>
       </c>
       <c r="J25" t="n">
-        <v>2.2865</v>
+        <v>0.1067</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2927</v>
+        <v>-0.1141</v>
       </c>
       <c r="L25" t="n">
-        <v>1.9939</v>
+        <v>0.2208</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1032</v>
+        <v>-0.5538</v>
       </c>
       <c r="N25" t="n">
-        <v>0.9005</v>
+        <v>-0.39</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0037</v>
+        <v>-0.1638</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R25" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2423</v>
+        <v>-0.0198</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4402</v>
+        <v>0.0356</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8022</v>
+        <v>-0.0553</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3943</v>
+        <v>-1.0722</v>
       </c>
       <c r="W25" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="26">
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>16.3082</v>
+        <v>17.8811</v>
       </c>
       <c r="E26" t="n">
-        <v>6.054600000000001</v>
+        <v>6.054399999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>10.2539</v>
+        <v>11.8265</v>
       </c>
       <c r="G26" t="n">
         <v>16.5999</v>
       </c>
       <c r="H26" t="n">
-        <v>4.7722</v>
+        <v>4.772199999999999</v>
       </c>
       <c r="I26" t="n">
         <v>11.8279</v>
@@ -2467,13 +2467,13 @@
         <v>-1.3389</v>
       </c>
       <c r="N26" t="n">
-        <v>0.8182</v>
+        <v>0.8182000000000001</v>
       </c>
       <c r="O26" t="n">
         <v>-2.1568</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.479200000000001</v>
+        <v>-3.4792</v>
       </c>
       <c r="Q26" t="n">
         <v>-24.3551</v>
@@ -2482,22 +2482,22 @@
         <v>20.8759</v>
       </c>
       <c r="S26" t="n">
-        <v>3.3607</v>
+        <v>4.9333</v>
       </c>
       <c r="T26" t="n">
         <v>4.2875</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9269000000000003</v>
+        <v>0.6458999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.1728999999999999</v>
+        <v>-0.1728999999999998</v>
       </c>
       <c r="W26" t="n">
         <v>8.183300000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.356199999999999</v>
+        <v>-8.356200000000001</v>
       </c>
     </row>
   </sheetData>
